--- a/Design/port peripheral mapping.xlsx
+++ b/Design/port peripheral mapping.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Hydra\Documents\DipTrace\Projects\MakerPnPControl\Design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB3FD206-B2A9-49AE-9618-2D5858734A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8701D1D-59AB-4909-BC7D-42866F842EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13785" yWindow="4335" windowWidth="29775" windowHeight="20505" activeTab="1" xr2:uid="{C3A3646F-069D-4AE0-AC21-8ACD43A56D36}"/>
+    <workbookView xWindow="38295" yWindow="0" windowWidth="19410" windowHeight="31785" activeTab="1" xr2:uid="{C3A3646F-069D-4AE0-AC21-8ACD43A56D36}"/>
   </bookViews>
   <sheets>
     <sheet name="UFBGA176+25 Ports" sheetId="5" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2123" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2123" uniqueCount="793">
   <si>
     <t>Port</t>
   </si>
@@ -2354,9 +2354,6 @@
   </si>
   <si>
     <t>Device only, connected to an on-board USB hub</t>
-  </si>
-  <si>
-    <t>WIFI + EXPANSION PORT</t>
   </si>
   <si>
     <t>Port 2 / EXPANSION PORT</t>
@@ -4113,7 +4110,7 @@
         <v>102</v>
       </c>
       <c r="C15" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D15" s="1" t="str">
         <f>_xlfn.XLOOKUP(_xlfn.CONCAT($A15,"_",D$2),'UFBGA176+25 GPIOs'!$B$1:$B$133,'UFBGA176+25 GPIOs'!$A$1:$A$133,"NONE")</f>
@@ -4176,7 +4173,7 @@
         <v>102</v>
       </c>
       <c r="C16" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D16" s="1" t="str">
         <f>_xlfn.XLOOKUP(_xlfn.CONCAT($A16,"_",D$2),'UFBGA176+25 GPIOs'!$B$1:$B$133,'UFBGA176+25 GPIOs'!$A$1:$A$133,"NONE")</f>
@@ -4368,7 +4365,7 @@
         <v>697</v>
       </c>
       <c r="C20" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D20" s="1" t="str">
         <f>_xlfn.XLOOKUP($A20,'UFBGA176+25 GPIOs'!$B$1:$B$133,'UFBGA176+25 GPIOs'!$A$1:$A$133)</f>
@@ -4383,7 +4380,7 @@
         <v>698</v>
       </c>
       <c r="C21" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D21" s="1" t="str">
         <f>_xlfn.XLOOKUP($A21,'UFBGA176+25 GPIOs'!$B$1:$B$133,'UFBGA176+25 GPIOs'!$A$1:$A$133)</f>
@@ -4486,7 +4483,7 @@
         <v>735</v>
       </c>
       <c r="C27" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="D27" s="1" t="str">
         <f>_xlfn.XLOOKUP(_xlfn.CONCAT($A27,"_",D$26),'UFBGA176+25 GPIOs'!$B$1:$B$133,'UFBGA176+25 GPIOs'!$A$1:$A$133)</f>
@@ -4854,7 +4851,7 @@
         <v>737</v>
       </c>
       <c r="C35" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D35" s="1" t="str">
         <f>_xlfn.XLOOKUP($A35,'UFBGA176+25 GPIOs'!$H$1:$H$133,'UFBGA176+25 GPIOs'!$A$1:$A$133)</f>
@@ -5011,7 +5008,7 @@
         <v>725</v>
       </c>
       <c r="B47" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C47" t="s">
         <v>92</v>
@@ -5090,10 +5087,10 @@
         <v>726</v>
       </c>
       <c r="B49" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C49" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D49" s="1" t="e">
         <f>_xlfn.XLOOKUP(_xlfn.CONCAT("OCTOSPIM_",D$48),'UFBGA176+25 GPIOs'!$B$1:$B$133,'UFBGA176+25 GPIOs'!$A$1:$A$133)</f>
@@ -5135,10 +5132,10 @@
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="B50" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C50" t="s">
         <v>759</v>
@@ -5150,13 +5147,13 @@
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B51" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C51" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>_xlfn.XLOOKUP($A51,'UFBGA176+25 GPIOs'!$H$1:$H$133,'UFBGA176+25 GPIOs'!$A$1:$A$133)</f>
@@ -5165,10 +5162,10 @@
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B52" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C52" t="s">
         <v>92</v>
@@ -5180,7 +5177,7 @@
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -5198,7 +5195,7 @@
         <v>149</v>
       </c>
       <c r="C55" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D55" s="1" t="str">
         <f>_xlfn.XLOOKUP($A55,'UFBGA176+25 GPIOs'!$B$1:$B$133,'UFBGA176+25 GPIOs'!$A$1:$A$133)</f>
@@ -6109,7 +6106,7 @@
         <v>374</v>
       </c>
       <c r="C95" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D95" t="str" cm="1">
         <f t="array" ref="D95" xml:space="preserve"> IF(C95&lt;&gt;"",
@@ -6125,7 +6122,7 @@
         <v>99</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="D96" t="str" cm="1">
         <f t="array" ref="D96" xml:space="preserve"> IF(C96&lt;&gt;"",
@@ -6148,7 +6145,7 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C98" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -6198,7 +6195,7 @@
         <v>106</v>
       </c>
       <c r="C105" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="D105" s="1" t="str">
         <f>_xlfn.XLOOKUP($A105,'UFBGA176+25 GPIOs'!$H$1:$H$133,'UFBGA176+25 GPIOs'!$A$1:$A$133)</f>
@@ -6210,7 +6207,7 @@
         <v>350</v>
       </c>
       <c r="C106" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D106" s="1" t="str">
         <f>_xlfn.XLOOKUP($A106,'UFBGA176+25 GPIOs'!$H$1:$H$133,'UFBGA176+25 GPIOs'!$A$1:$A$133)</f>
@@ -6222,7 +6219,7 @@
         <v>349</v>
       </c>
       <c r="C107" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="D107" s="1" t="str">
         <f>_xlfn.XLOOKUP($A107,'UFBGA176+25 GPIOs'!$H$1:$H$133,'UFBGA176+25 GPIOs'!$A$1:$A$133)</f>
@@ -6234,7 +6231,7 @@
         <v>351</v>
       </c>
       <c r="C108" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>_xlfn.XLOOKUP($A108,'UFBGA176+25 GPIOs'!$H$1:$H$133,'UFBGA176+25 GPIOs'!$A$1:$A$133)</f>
@@ -6246,7 +6243,7 @@
         <v>702</v>
       </c>
       <c r="C109" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>_xlfn.XLOOKUP($A109,'UFBGA176+25 GPIOs'!$H$1:$H$133,'UFBGA176+25 GPIOs'!$A$1:$A$133)</f>
@@ -6258,7 +6255,7 @@
         <v>700</v>
       </c>
       <c r="C110" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>_xlfn.XLOOKUP($A110,'UFBGA176+25 GPIOs'!$H$1:$H$133,'UFBGA176+25 GPIOs'!$A$1:$A$133)</f>
@@ -7935,7 +7932,7 @@
         <v>136</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="I52" s="1" t="b">
         <v>1</v>
@@ -7964,7 +7961,7 @@
         <v>136</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="I53" s="1" t="b">
         <v>1</v>
@@ -8832,7 +8829,7 @@
         <v>136</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="I85" s="1" t="b">
         <v>1</v>
@@ -9766,7 +9763,7 @@
         <v>136</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="I119" s="1" t="b">
         <v>1</v>
@@ -10150,7 +10147,7 @@
         <v>136</v>
       </c>
       <c r="H133" s="1" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="I133" s="1" t="b">
         <v>1</v>
@@ -10784,7 +10781,7 @@
         <v>461</v>
       </c>
       <c r="E36" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="J36" t="s">
         <v>537</v>
@@ -10805,7 +10802,7 @@
         <v>462</v>
       </c>
       <c r="E37" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="J37" t="s">
         <v>537</v>
@@ -10816,7 +10813,7 @@
         <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C38">
         <f t="shared" si="0"/>
@@ -10829,7 +10826,7 @@
         <v>449</v>
       </c>
       <c r="F38" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="J38" t="s">
         <v>537</v>
@@ -10840,7 +10837,7 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C39">
         <f t="shared" si="0"/>
@@ -10853,7 +10850,7 @@
         <v>92</v>
       </c>
       <c r="G39" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="J39" t="s">
         <v>537</v>
@@ -14690,7 +14687,7 @@
         <v>AMUX_EN</v>
       </c>
       <c r="C157" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -14699,7 +14696,7 @@
         <v>AMUX_A0</v>
       </c>
       <c r="C158" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -14708,7 +14705,7 @@
         <v>AMUX_A1</v>
       </c>
       <c r="C159" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
   </sheetData>

--- a/Design/port peripheral mapping.xlsx
+++ b/Design/port peripheral mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Hydra\Documents\DipTrace\Projects\MakerPnPControl\Design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8701D1D-59AB-4909-BC7D-42866F842EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE69C2A4-8F4F-421A-B0E6-59F2DE94EDDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38295" yWindow="0" windowWidth="19410" windowHeight="31785" activeTab="1" xr2:uid="{C3A3646F-069D-4AE0-AC21-8ACD43A56D36}"/>
+    <workbookView xWindow="18165" yWindow="11970" windowWidth="23340" windowHeight="16140" xr2:uid="{C3A3646F-069D-4AE0-AC21-8ACD43A56D36}"/>
   </bookViews>
   <sheets>
     <sheet name="UFBGA176+25 Ports" sheetId="5" r:id="rId1"/>
@@ -3009,11 +3009,11 @@
         <v>0,1,5,6</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" t="str">
         <f>_xlfn.XLOOKUP(D3,'UFBFA176+25 Peripherals'!$A:$A,'UFBFA176+25 Peripherals'!$I:$I,"N/A")</f>
-        <v>0,1,2,3</v>
+        <v>11,12,13,14</v>
       </c>
       <c r="F3" t="s">
         <v>397</v>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="N3" t="str">
         <f>_xlfn.TEXTJOIN(",",,_xlfn.TAKE(_xlfn.TEXTSPLIT(C3,","),,-2),_xlfn.TAKE(_xlfn.TEXTSPLIT(E3,","),,-2))</f>
-        <v>5,6,2,3</v>
+        <v>5,6,13,14</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -3109,11 +3109,11 @@
         <v>6,7,14,15</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" t="str">
         <f>_xlfn.XLOOKUP(D5,'UFBFA176+25 Peripherals'!$A:$A,'UFBFA176+25 Peripherals'!$I:$I,"N/A")</f>
-        <v>11,12,13,14</v>
+        <v>0,1,2,3</v>
       </c>
       <c r="F5" t="s">
         <v>396</v>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="N5" t="str">
         <f>_xlfn.TEXTJOIN(",",,_xlfn.TAKE(_xlfn.TEXTSPLIT(C5,","),,-2),_xlfn.TAKE(_xlfn.TEXTSPLIT(E5,","),,-2))</f>
-        <v>14,15,13,14</v>
+        <v>14,15,2,3</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">

--- a/Design/port peripheral mapping.xlsx
+++ b/Design/port peripheral mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Hydra\Documents\DipTrace\Projects\MakerPnPControl\Design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE69C2A4-8F4F-421A-B0E6-59F2DE94EDDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC6D221-5394-4C86-B5B3-B77B4C476533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18165" yWindow="11970" windowWidth="23340" windowHeight="16140" xr2:uid="{C3A3646F-069D-4AE0-AC21-8ACD43A56D36}"/>
+    <workbookView xWindow="14475" yWindow="14790" windowWidth="23340" windowHeight="16140" xr2:uid="{C3A3646F-069D-4AE0-AC21-8ACD43A56D36}"/>
   </bookViews>
   <sheets>
     <sheet name="UFBGA176+25 Ports" sheetId="5" r:id="rId1"/>

--- a/Design/port peripheral mapping.xlsx
+++ b/Design/port peripheral mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Hydra\Documents\DipTrace\Projects\MakerPnPControl\Design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC6D221-5394-4C86-B5B3-B77B4C476533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B4F2D4A-B682-44D8-9EBD-12BC5AE85E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14475" yWindow="14790" windowWidth="23340" windowHeight="16140" xr2:uid="{C3A3646F-069D-4AE0-AC21-8ACD43A56D36}"/>
+    <workbookView xWindow="24795" yWindow="12810" windowWidth="23340" windowHeight="16140" activeTab="1" xr2:uid="{C3A3646F-069D-4AE0-AC21-8ACD43A56D36}"/>
   </bookViews>
   <sheets>
     <sheet name="UFBGA176+25 Ports" sheetId="5" r:id="rId1"/>
@@ -2374,9 +2374,6 @@
     <t>OCTOSPI2_NCS_3</t>
   </si>
   <si>
-    <t>FLASH - NCS to flash</t>
-  </si>
-  <si>
     <t>EXPANSION_PORT</t>
   </si>
   <si>
@@ -2447,6 +2444,9 @@
   </si>
   <si>
     <t>TCXO, single pin</t>
+  </si>
+  <si>
+    <t>FLASH - NCS to flash and ESP32-C6 FSPIQ and FPGA SPI_SS_B</t>
   </si>
 </sst>
 </file>
@@ -5008,7 +5008,7 @@
         <v>725</v>
       </c>
       <c r="B47" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C47" t="s">
         <v>92</v>
@@ -5087,10 +5087,10 @@
         <v>726</v>
       </c>
       <c r="B49" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C49" t="s">
-        <v>768</v>
+        <v>792</v>
       </c>
       <c r="D49" s="1" t="e">
         <f>_xlfn.XLOOKUP(_xlfn.CONCAT("OCTOSPIM_",D$48),'UFBGA176+25 GPIOs'!$B$1:$B$133,'UFBGA176+25 GPIOs'!$A$1:$A$133)</f>
@@ -5135,7 +5135,7 @@
         <v>766</v>
       </c>
       <c r="B50" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C50" t="s">
         <v>759</v>
@@ -5150,10 +5150,10 @@
         <v>767</v>
       </c>
       <c r="B51" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C51" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>_xlfn.XLOOKUP($A51,'UFBGA176+25 GPIOs'!$H$1:$H$133,'UFBGA176+25 GPIOs'!$A$1:$A$133)</f>
@@ -5162,10 +5162,10 @@
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B52" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C52" t="s">
         <v>92</v>
@@ -5177,7 +5177,7 @@
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -5195,7 +5195,7 @@
         <v>149</v>
       </c>
       <c r="C55" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="D55" s="1" t="str">
         <f>_xlfn.XLOOKUP($A55,'UFBGA176+25 GPIOs'!$B$1:$B$133,'UFBGA176+25 GPIOs'!$A$1:$A$133)</f>
@@ -6106,7 +6106,7 @@
         <v>374</v>
       </c>
       <c r="C95" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="D95" t="str" cm="1">
         <f t="array" ref="D95" xml:space="preserve"> IF(C95&lt;&gt;"",
@@ -6122,7 +6122,7 @@
         <v>99</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D96" t="str" cm="1">
         <f t="array" ref="D96" xml:space="preserve"> IF(C96&lt;&gt;"",
@@ -6145,7 +6145,7 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="C98" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -6195,7 +6195,7 @@
         <v>106</v>
       </c>
       <c r="C105" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="D105" s="1" t="str">
         <f>_xlfn.XLOOKUP($A105,'UFBGA176+25 GPIOs'!$H$1:$H$133,'UFBGA176+25 GPIOs'!$A$1:$A$133)</f>
@@ -6207,7 +6207,7 @@
         <v>350</v>
       </c>
       <c r="C106" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="D106" s="1" t="str">
         <f>_xlfn.XLOOKUP($A106,'UFBGA176+25 GPIOs'!$H$1:$H$133,'UFBGA176+25 GPIOs'!$A$1:$A$133)</f>
@@ -6219,7 +6219,7 @@
         <v>349</v>
       </c>
       <c r="C107" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="D107" s="1" t="str">
         <f>_xlfn.XLOOKUP($A107,'UFBGA176+25 GPIOs'!$H$1:$H$133,'UFBGA176+25 GPIOs'!$A$1:$A$133)</f>
@@ -6231,7 +6231,7 @@
         <v>351</v>
       </c>
       <c r="C108" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>_xlfn.XLOOKUP($A108,'UFBGA176+25 GPIOs'!$H$1:$H$133,'UFBGA176+25 GPIOs'!$A$1:$A$133)</f>
@@ -6243,7 +6243,7 @@
         <v>702</v>
       </c>
       <c r="C109" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>_xlfn.XLOOKUP($A109,'UFBGA176+25 GPIOs'!$H$1:$H$133,'UFBGA176+25 GPIOs'!$A$1:$A$133)</f>
@@ -6255,7 +6255,7 @@
         <v>700</v>
       </c>
       <c r="C110" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>_xlfn.XLOOKUP($A110,'UFBGA176+25 GPIOs'!$H$1:$H$133,'UFBGA176+25 GPIOs'!$A$1:$A$133)</f>
@@ -7932,7 +7932,7 @@
         <v>136</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="I52" s="1" t="b">
         <v>1</v>
@@ -7961,7 +7961,7 @@
         <v>136</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="I53" s="1" t="b">
         <v>1</v>
@@ -9763,7 +9763,7 @@
         <v>136</v>
       </c>
       <c r="H119" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="I119" s="1" t="b">
         <v>1</v>
@@ -10781,7 +10781,7 @@
         <v>461</v>
       </c>
       <c r="E36" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="J36" t="s">
         <v>537</v>
@@ -10802,7 +10802,7 @@
         <v>462</v>
       </c>
       <c r="E37" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="J37" t="s">
         <v>537</v>
@@ -10813,7 +10813,7 @@
         <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C38">
         <f t="shared" si="0"/>
@@ -10826,7 +10826,7 @@
         <v>449</v>
       </c>
       <c r="F38" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="J38" t="s">
         <v>537</v>
@@ -10837,7 +10837,7 @@
         <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C39">
         <f t="shared" si="0"/>
@@ -10850,7 +10850,7 @@
         <v>92</v>
       </c>
       <c r="G39" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="J39" t="s">
         <v>537</v>
@@ -14687,7 +14687,7 @@
         <v>AMUX_EN</v>
       </c>
       <c r="C157" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -14696,7 +14696,7 @@
         <v>AMUX_A0</v>
       </c>
       <c r="C158" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -14705,7 +14705,7 @@
         <v>AMUX_A1</v>
       </c>
       <c r="C159" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
   </sheetData>
